--- a/src/translations.xlsx
+++ b/src/translations.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="49">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -85,34 +85,7 @@
     <t xml:space="preserve">meta_funded_by</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Noto Sans Mono"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">&lt;a href="</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Noto Sans Mono"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">https://www.text-plus.org/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Noto Sans Mono"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">"&gt;TEXT+&lt;/a&gt;</t>
-    </r>
+    <t xml:space="preserve">&lt;a href="https://www.text-plus.org/"&gt;TEXT+&lt;/a&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">meta_distributor</t>
@@ -167,6 +140,36 @@
   </si>
   <si>
     <t xml:space="preserve">&lt;a href="https://creativecommons.org/licenses/by/4.0/"&gt;Creative Commons License CC-BY 4.0 (Attribution 4.0 International)&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">language</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sprache</t>
+  </si>
+  <si>
+    <t xml:space="preserve">date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Datum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">signatories</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vertragspartner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">locations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quelle</t>
   </si>
 </sst>
 </file>
@@ -269,7 +272,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -299,6 +302,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -425,7 +432,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="19" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="33.57"/>
@@ -434,7 +441,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="4" style="3" width="11.53"/>
   </cols>
   <sheetData>
-    <row r="1" s="6" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="6" customFormat="true" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -443,7 +450,7 @@
       </c>
       <c r="C1" s="4"/>
     </row>
-    <row r="2" customFormat="false" ht="38.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -451,7 +458,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -459,7 +466,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -467,7 +474,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -475,7 +482,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -483,7 +490,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="301.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="297" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
@@ -491,7 +498,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
@@ -499,7 +506,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="235.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="231.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
@@ -507,7 +514,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="317.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="313.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
@@ -515,15 +522,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="38.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="8" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="71.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="67.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
         <v>21</v>
       </c>
@@ -531,7 +538,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="71.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="67.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
         <v>23</v>
       </c>
@@ -539,7 +546,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
         <v>25</v>
       </c>
@@ -547,7 +554,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="38.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
         <v>27</v>
       </c>
@@ -555,7 +562,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
         <v>29</v>
       </c>
@@ -563,7 +570,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
         <v>31</v>
       </c>
@@ -571,7 +578,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
         <v>32</v>
       </c>
@@ -579,7 +586,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
         <v>33</v>
       </c>
@@ -587,7 +594,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
         <v>35</v>
       </c>
@@ -595,7 +602,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
         <v>36</v>
       </c>
@@ -603,7 +610,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="88.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="83.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
         <v>37</v>
       </c>
@@ -611,9 +618,49 @@
         <v>38</v>
       </c>
     </row>
+    <row r="23" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B11" r:id="rId1" display="https://www.text-plus.org/"/>
+    <hyperlink ref="B11" r:id="rId1" display="&lt;a href=&quot;https://www.text-plus.org/&quot;&gt;TEXT+&lt;/a&gt;"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/src/translations.xlsx
+++ b/src/translations.xlsx
@@ -10,7 +10,7 @@
   <sheets>
     <sheet name="translations" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="64">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -28,6 +28,9 @@
     <t xml:space="preserve">de</t>
   </si>
   <si>
+    <t xml:space="preserve">OLD</t>
+  </si>
+  <si>
     <t xml:space="preserve">super_title</t>
   </si>
   <si>
@@ -58,6 +61,9 @@
     <t xml:space="preserve">super_text</t>
   </si>
   <si>
+    <t xml:space="preserve">Diese Website bietet Zugang zu den Daten von mehr als 1800 frühneuzeitlichen europäischen Friedensverträgen. Die Daten wurden im Rahmen des Legacy-Projekts &lt;a href="https://www.ieg-friedensvertraege.de/Startseite------_site.index..html_dir._nav.2_likecms.html"&gt;Europäische Friedensverträge der Vormoderne online&lt;/a&gt; gesammelt. Im Jahr 2023 wurden diese Daten im Rahmen des Projekts &lt;a href="https://www.ieg-friedensvertraege.de/friverplus"&gt;Europäische Friedensverträge der Vormoderne in Daten (FriVer+)&lt;/a&gt; in XML umgewandelt. Die Daten umfassen digitale Surrogate, Metadaten und in einer begrenzten Anzahl von Fällen auch Editionen und Transliterationen der Texte.</t>
+  </si>
+  <si>
     <t xml:space="preserve">This site provides access to data pertaining to more than 1800 early modern European peace treaties. The data was gathered by the legacy project &lt;a href="https://www.ieg-friedensvertraege.de/Startseite------_site.index..html_dir._nav.2_likecms.html"&gt;Europäische Friedensverträge der Vormoderne online&lt;/a&gt; (2005-2010). In 2023 this data was transformed into XML as part of the &lt;a href="https://www.ieg-friedensvertraege.de/friverplus"&gt;Europäische Friedensverträge der Vormoderne in Daten (FriVer+)&lt;/a&gt; project. The data comprises digital surrogates, metadata, and, in a more limited number of cases, editions and transliterations of the texts as well.</t>
   </si>
   <si>
@@ -70,14 +76,21 @@
     <t xml:space="preserve">friverplus_description</t>
   </si>
   <si>
-    <t xml:space="preserve">Lorem ipsum dolor sit amet, consectetur adipiscing elit, sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco &lt;a href="https://google.com"&gt;laboris nisi ut&lt;/a&gt; aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse &lt;a href="heise.de"&gt;cillum&lt;/a&gt; dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum.</t>
+    <t xml:space="preserve">Das FriVer+ Projekt hat den &lt;a href="https://www.go-fair.org/fair-principles/"&gt;FAIR-Prinzipien&lt;/a&gt; folgend die Daten auf der Webseite &lt;a href="https://www.ieg-friedensvertraege.de/Startseite------_site.index..html_dir._nav.2_likecms.html"&gt;Europäische Friedensverträge der Vormoderne online&lt;/a&gt; transformiert. Diese Webseite stellt Informationen über insgesamt 1800 Europäische Friedensverträge aus dem Zeitraum zwischen 1400 und 1789 zur Verfügung. Die Daten umfassen Digitalisate, Metadaten, und, in einer begrenzteren Anzahl von Fällen, auch Transkriptionen und Editionen der Texte, und sind in einer relationalen Datenbank gespeichert. Über Abfragen auf der Website können die Daten aus dieser Datenbank abgerufen werden, aber der Zugriff auf die Rohdaten ist nicht so einfach, wie er heutzutage idealerweise sein sollte. Um die Auffindbarkeit und den Zugang zu diesen Daten zu verbessern, sind sie aus der Datenbank exportiert und in XML gemäß dem &lt;a href="https://tei-c.org/"&gt;TEI-Schema&lt;/a&gt; umgewandelt. Die Verwendung dieses Schemas und die Aufnahme der umgewandelten Daten in öffentliche und frei zugängliche Repositorien (nämlich &lt;a href="https://github.com/ieg-dhr/friver-plus&gt;hier&lt;/a&gt; und &lt;a href="https://exist.ulb.tu-darmstadt.de/2/v/pa000299"&gt;hier&lt;/a&gt;) stellen sicher, dass die Daten von Wissenschaftler:innen aus verschiedenen Disziplinen einfacher genutzt und wiederverwendet werden können, wodurch die Erforschung von (frühneuzeitlichen) Friedensverträgen unterstützt wird.
+Das Projekt, das vom NFDI-Konsortium &lt;a href="https://www.text-plus.org/&gt;Text +&lt;/a&gt; als Kooperationsprojekt finanziert wurde, lief bis Ende 2023.</t>
   </si>
   <si>
     <t xml:space="preserve">meta_editor</t>
   </si>
   <si>
     <t xml:space="preserve">Jaap Geraerts&lt;br /&gt;&lt;br /&gt;
-&lt;em&gt;The transformation and enrichment of the data is done by Jaap Geraerts (IEG Mainz). The other members of the FriVer+ team are Fabian Cremer, Ines Grund, and Thorsten Wübbena (all IEG Mainz).&lt;br /&gt;&lt;br /&gt;
+&lt;em&gt;Die Transformation und Anreicherung der Daten wurden von Jaap Geraerts (IEG Mainz) durchgeführt. Die anderen Mitglieder des FriVer+-Teams waren Fabian Cremer, Ines Grund und Thorsten Wübbena (alle IEG Mainz).&lt;br /&gt;&lt;br /&gt;
+Die Originaldaten wurden von dem &lt;a href="https://www.ieg-friedensvertraege.de"&gt;Wissenschaftlerteam&lt;/a&gt; im Rahmen des Projekts Europäische Friedensverträge der Vormoderne erstellt. Dieses Projekt wurde von Prof. Dr. Heinz Duchhardt geleitet und war am Leibniz-Institut für Europäische Geschichte in Mainz angesiedelt.
+&lt;/em&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaap Geraerts&lt;br /&gt;&lt;br /&gt;
+&lt;em&gt;The transformation and enrichment of the data was done by Jaap Geraerts (IEG Mainz). The other members of the FriVer+ team were Fabian Cremer, Ines Grund, and Thorsten Wübbena (all IEG Mainz).&lt;br /&gt;&lt;br /&gt;
 The original data has been created by the &lt;a href="https://www.ieg-friedensvertraege.de"&gt;team of scholars&lt;/a&gt; who were part of the Europäische Friedensverträge der Vormoderne project. This project was lead by Prof. Dr. Heinz Duchhardt and was based at the Leibniz Institute of European History in Mainz.
 &lt;/em&gt;</t>
   </si>
@@ -109,33 +122,57 @@
     <t xml:space="preserve">meta_what</t>
   </si>
   <si>
+    <t xml:space="preserve">Digitale Edition nach &lt;a href="http://www.tei-c.org/"&gt;TEI P5&lt;/a&gt;</t>
+  </si>
+  <si>
     <t xml:space="preserve">Digital edition according to &lt;a href="http://www.tei-c.org/"&gt;TEI P5&lt;/a&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">funded_by</t>
   </si>
   <si>
+    <t xml:space="preserve">finanziert von</t>
+  </si>
+  <si>
     <t xml:space="preserve">funded by</t>
   </si>
   <si>
     <t xml:space="preserve">distributor</t>
   </si>
   <si>
+    <t xml:space="preserve">Hosting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hosting</t>
+  </si>
+  <si>
     <t xml:space="preserve">publisher</t>
   </si>
   <si>
+    <t xml:space="preserve">Herausgeber</t>
+  </si>
+  <si>
     <t xml:space="preserve">issued_on</t>
   </si>
   <si>
+    <t xml:space="preserve">veröffentlicht am</t>
+  </si>
+  <si>
     <t xml:space="preserve">issued on</t>
   </si>
   <si>
     <t xml:space="preserve">editor</t>
   </si>
   <si>
+    <t xml:space="preserve">Editor</t>
+  </si>
+  <si>
     <t xml:space="preserve">license</t>
   </si>
   <si>
+    <t xml:space="preserve">Lizenz</t>
+  </si>
+  <si>
     <t xml:space="preserve">meta_license</t>
   </si>
   <si>
@@ -170,6 +207,47 @@
   </si>
   <si>
     <t xml:space="preserve">Quelle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">imprint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impressum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">imprint_text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Herausgegeben für das Leibniz-Institut für Europäische Geschichte (IEG)&lt;br&gt;
+von Joachim Berger, Irene Dingel und Johannes Paulmann&lt;br&gt;
+Mainz 2016–2023.&lt;br&gt;
+URL: &lt;a href="https://ieg-differences.eu/"&gt;https://ieg-differences.eu&lt;/a&gt;&lt;/p&gt;
+&lt;p&gt;Textredaktion: Joachim Berger&lt;br&gt;
+Normdaten, Verschlagwortung: Ines Grund&lt;br&gt;
+Konzeptionelle Mitarbeit: Sarah Panter&lt;/p&gt;
+&lt;p&gt;Texte der Vorschauartikel, WordPress-Redaktion: Sabine Gruler, Kirsten Wagner&lt;br&gt;
+&lt;a href="http://www.kultourkonzepte.de/"&gt;http://www.kultourkonzepte.de&lt;/a&gt;&lt;/p&gt;
+&lt;p&gt;Übersetzungen: Patrick Baker, Ellen Glebe, Christopher Reid, Niall Williams&lt;/p&gt;
+&lt;p&gt;Datenkuration, Projektleitung Langzeitverfügbarkeit: Fabian Cremer, Thorsten Wübbena&lt;/p&gt;
+&lt;p class="mt-7"&gt;&lt;strong&gt;Angaben gemäß § 5 TMG&lt;/strong&gt;&lt;/p&gt;
+&lt;p class="mt-4"&gt;&lt;em&gt;Herausgebende Institution&lt;/em&gt;&lt;/p&gt;
+&lt;p&gt;Leibniz-Institut für Europäische Geschichte (IEG)&lt;br&gt;
+Alte Universitätsstraße 19&lt;br&gt;
+D-55116 Mainz&lt;br&gt;
+&lt;a href="http://www.ieg-mainz.de"&gt;http://www.ieg-mainz.de&lt;/a&gt;
+&lt;a href="mailto:info@ieg-mainz.de"&gt;info@ieg-mainz.de&lt;/a&gt;
+Telefon: ++49 (0) 6131 39 393 50&lt;br&gt;
+Fax: ++ 49 (0) 6131 39 353 26&lt;/p&gt;
+&lt;p class="mt-5"&gt;&lt;em&gt;Verantwortlich für den Inhalt&lt;/em&gt;&lt;/p&gt;
+&lt;p&gt;Prof. Dr. Nicole Reinhardt, Prof. Dr. Johannes Paulmann&lt;/p&gt;
+&lt;p class="mt-5"&gt;&lt;em&gt;Programming and Design&lt;/em&gt;&lt;/p&gt;
+&lt;p&gt;Wendig OÜ&lt;br&gt;
+&lt;a href="https://wendig.io"&gt;https://wendig.io&lt;/a&gt;&lt;/p&gt;
+&lt;p class="mt-5"&gt;&lt;em&gt;Rechtliche Hinweise&lt;/em&gt;&lt;/p&gt;
+&lt;p&gt;„Ortstermine. Umgang mit Differenz in Europa“ wird gemäß deutschem Urheberrecht publiziert, dessen Schutzdauer die international vereinbarte Mindestschutzfrist der Revidierten Berner Übereinkunft (RBÜ) überschreitet und gemäß EU-Recht auf 70 Jahre nach Tod des Urhebers verlängert. Das IEG prüft sorgfältig sämtliche Rechte zur Speicherung und Veröffentlichung von urheberrechtlich geschütztem Material. Urheberrechtlich geschütztes Material, für das keine Rechteklärung erfolgen kann, wird nicht in „Ortstermine“ gespeichert oder veröffentlicht.&lt;/p&gt;
+&lt;p class="mt-5"&gt;&lt;em&gt;Haftungsausschluss&lt;/em&gt;&lt;/p&gt;
+&lt;p&gt;Trotz sorgfältiger inhaltlicher Kontrolle übernimmt die herausgebende Institution keine Haftung für die Inhalte externer Links. Für den Inhalt der verlinkten Seiten sind ausschließlich deren Betreiber verantwortlich.&lt;/p&gt;
+</t>
   </si>
 </sst>
 </file>
@@ -180,7 +258,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -213,6 +291,12 @@
       <sz val="12"/>
       <name val="Noto Sans Mono"/>
       <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Noto Sans Mono"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
@@ -272,40 +356,48 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -432,230 +524,277 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="19" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:C29"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="33.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="54.95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="23.09"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="4" style="3" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="33.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="94.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="53.29"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="11.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="83"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="6" style="3" width="11.43"/>
   </cols>
   <sheetData>
-    <row r="1" s="6" customFormat="true" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="6" customFormat="true" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4"/>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>2023</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="297" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="313.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>13</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="231.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="773.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="313.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="288.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>20</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="67.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="67.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>30</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>33</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>36</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>39</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>41</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>44</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>36</v>
+        <v>46</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="83.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>48</v>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="1035.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/src/translations.xlsx
+++ b/src/translations.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="70">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -218,36 +218,50 @@
     <t xml:space="preserve">imprint_text</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;p&gt;Herausgegeben für das Leibniz-Institut für Europäische Geschichte (IEG)&lt;br&gt;
-von Joachim Berger, Irene Dingel und Johannes Paulmann&lt;br&gt;
-Mainz 2016–2023.&lt;br&gt;
-URL: &lt;a href="https://ieg-differences.eu/"&gt;https://ieg-differences.eu&lt;/a&gt;&lt;/p&gt;
-&lt;p&gt;Textredaktion: Joachim Berger&lt;br&gt;
-Normdaten, Verschlagwortung: Ines Grund&lt;br&gt;
-Konzeptionelle Mitarbeit: Sarah Panter&lt;/p&gt;
-&lt;p&gt;Texte der Vorschauartikel, WordPress-Redaktion: Sabine Gruler, Kirsten Wagner&lt;br&gt;
-&lt;a href="http://www.kultourkonzepte.de/"&gt;http://www.kultourkonzepte.de&lt;/a&gt;&lt;/p&gt;
-&lt;p&gt;Übersetzungen: Patrick Baker, Ellen Glebe, Christopher Reid, Niall Williams&lt;/p&gt;
-&lt;p&gt;Datenkuration, Projektleitung Langzeitverfügbarkeit: Fabian Cremer, Thorsten Wübbena&lt;/p&gt;
+    <t xml:space="preserve">&lt;p class="mt-4"&gt;&lt;em&gt;Herausgebende Institution&lt;/em&gt;&lt;/p&gt;
+&lt;p&gt;Leibniz-Institut für Europäische Geschichte (IEG)&lt;br&gt;
+Alte Universitätsstraße 19&lt;br&gt;
+D-55116 Mainz&lt;br&gt;
+&lt;p&gt;Gefördert im Rahmen der 2. Ausschreibungsrunde (2023) „Kooperationsprojekte“ des NFDI-Konsortiums text+ (&lt;a href="https://text-plus.org"&gt;https://text-plus.org&lt;/a&gt;)&lt;/p&gt;
+&lt;p class="mt-4"&gt;&lt;em&gt;Projektteam am IEG&lt;/em&gt;&lt;/p&gt;
+&lt;p&gt;Editorische Verantwortung, Datenbereinigung, -transformation, -anreicherung: Dr. Jaap Geraerts&lt;/p&gt;
+&lt;p&gt;Langzeitverfügbarkeit: Fabian Cremer&lt;/p&gt;
+&lt;p&gt;Projektleitung: Thorsten Wübbena&lt;/p&gt;
 &lt;p class="mt-7"&gt;&lt;strong&gt;Angaben gemäß § 5 TMG&lt;/strong&gt;&lt;/p&gt;
-&lt;p class="mt-4"&gt;&lt;em&gt;Herausgebende Institution&lt;/em&gt;&lt;/p&gt;
+&lt;p class="mt-5"&gt;&lt;em&gt;Verantwortlich für den Inhalt&lt;/em&gt;&lt;/p&gt;
 &lt;p&gt;Leibniz-Institut für Europäische Geschichte (IEG)&lt;br&gt;
 Alte Universitätsstraße 19&lt;br&gt;
 D-55116 Mainz&lt;br&gt;
 &lt;a href="http://www.ieg-mainz.de"&gt;http://www.ieg-mainz.de&lt;/a&gt;
-&lt;a href="mailto:info@ieg-mainz.de"&gt;info@ieg-mainz.de&lt;/a&gt;
+&lt;a href="mailto:info@ieg-mainz.de"&gt;info@ieg-mainz.de&lt;/a&gt;&lt;br /&gt;
 Telefon: ++49 (0) 6131 39 393 50&lt;br&gt;
 Fax: ++ 49 (0) 6131 39 353 26&lt;/p&gt;
-&lt;p class="mt-5"&gt;&lt;em&gt;Verantwortlich für den Inhalt&lt;/em&gt;&lt;/p&gt;
 &lt;p&gt;Prof. Dr. Nicole Reinhardt, Prof. Dr. Johannes Paulmann&lt;/p&gt;
 &lt;p class="mt-5"&gt;&lt;em&gt;Programming and Design&lt;/em&gt;&lt;/p&gt;
 &lt;p&gt;Wendig OÜ&lt;br&gt;
 &lt;a href="https://wendig.io"&gt;https://wendig.io&lt;/a&gt;&lt;/p&gt;
 &lt;p class="mt-5"&gt;&lt;em&gt;Rechtliche Hinweise&lt;/em&gt;&lt;/p&gt;
-&lt;p&gt;„Ortstermine. Umgang mit Differenz in Europa“ wird gemäß deutschem Urheberrecht publiziert, dessen Schutzdauer die international vereinbarte Mindestschutzfrist der Revidierten Berner Übereinkunft (RBÜ) überschreitet und gemäß EU-Recht auf 70 Jahre nach Tod des Urhebers verlängert. Das IEG prüft sorgfältig sämtliche Rechte zur Speicherung und Veröffentlichung von urheberrechtlich geschütztem Material. Urheberrechtlich geschütztes Material, für das keine Rechteklärung erfolgen kann, wird nicht in „Ortstermine“ gespeichert oder veröffentlicht.&lt;/p&gt;
+&lt;p&gt;„Europäische Friedensverträge der Vormoderne in Daten (FriVer+)“ wird gemäß deutschem Urheberrecht publiziert, dessen Schutzdauer die international vereinbarte Mindestschutzfrist der Revidierten Berner Übereinkunft (RBÜ) überschreitet und gemäß EU-Recht auf 70 Jahre nach Tod des Urhebers verlängert. Das IEG prüft sorgfältig sämtliche Rechte zur Speicherung und Veröffentlichung von urheberrechtlich geschütztem Material. Urheberrechtlich geschütztes Material, für das keine Rechteklärung erfolgen kann, wird nicht in „Ortstermine“ gespeichert oder veröffentlicht.&lt;/p&gt;
 &lt;p class="mt-5"&gt;&lt;em&gt;Haftungsausschluss&lt;/em&gt;&lt;/p&gt;
-&lt;p&gt;Trotz sorgfältiger inhaltlicher Kontrolle übernimmt die herausgebende Institution keine Haftung für die Inhalte externer Links. Für den Inhalt der verlinkten Seiten sind ausschließlich deren Betreiber verantwortlich.&lt;/p&gt;
-</t>
+&lt;p&gt;Trotz sorgfältiger inhaltlicher Kontrolle übernimmt die herausgebende Institution keine Haftung für die Inhalte externer Links. Für den Inhalt der verlinkten Seiten sind ausschließlich deren Betreiber verantwortlich.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">privacy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Datenschutz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">edition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">transliteration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transkription</t>
   </si>
 </sst>
 </file>
@@ -258,7 +272,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -306,6 +320,13 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0000FF"/>
+      <name val="Noto Sans Mono"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -356,48 +377,52 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -524,15 +549,15 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:C32"/>
+  <sheetFormatPr defaultColWidth="11.5078125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="33.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="94.46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="53.29"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="11.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="33.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="119.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="53.33"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="11.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="83"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="6" style="3" width="11.43"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="6" style="3" width="11.5"/>
   </cols>
   <sheetData>
     <row r="1" s="6" customFormat="true" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -546,7 +571,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -578,7 +603,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
@@ -605,7 +630,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="773.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="346.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
         <v>17</v>
       </c>
@@ -632,7 +657,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="67.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="33.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
         <v>24</v>
       </c>
@@ -640,7 +665,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="67.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="33.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
         <v>26</v>
       </c>
@@ -656,7 +681,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="33.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
         <v>30</v>
       </c>
@@ -733,7 +758,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="83.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="33.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
         <v>48</v>
       </c>
@@ -741,7 +766,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
         <v>50</v>
       </c>
@@ -749,7 +774,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
         <v>52</v>
       </c>
@@ -757,7 +782,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
         <v>54</v>
       </c>
@@ -765,7 +790,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
         <v>56</v>
       </c>
@@ -773,7 +798,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
         <v>58</v>
       </c>
@@ -781,7 +806,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
         <v>60</v>
       </c>
@@ -789,17 +814,42 @@
         <v>61</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="1035.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="408.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="B29" s="11" t="s">
         <v>63</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B11" r:id="rId1" display="&lt;a href=&quot;https://www.text-plus.org/&quot;&gt;TEXT+&lt;/a&gt;"/>
+    <hyperlink ref="B29" r:id="rId2" display="&lt;p class=&quot;mt-4&quot;&gt;&lt;em&gt;Herausgebende Institution&lt;/em&gt;&lt;/p&gt;&#10;&#10;&lt;p&gt;Leibniz-Institut für Europäische Geschichte (IEG)&lt;br&gt;&#10;Alte Universitätsstraße 19&lt;br&gt;&#10;D-55116 Mainz&lt;br&gt;&#10;&#10;&lt;p&gt;Gefördert im Rahmen der 2. Ausschreibungsrunde (2023) „Kooperationsprojekte“ des NFDI-Konsortiums text+ (&lt;a href=&quot;https://text-plus.org&quot;&gt;https://text-plus.org&lt;/a&gt;)&lt;/p&gt;&#10;&#10;&lt;p class=&quot;mt-4&quot;&gt;&lt;em&gt;Projektteam am IEG&lt;/em&gt;&lt;/p&gt;&#10;&#10;&lt;p&gt;Editorische Verantwortung, Datenbereinigung, -transformation, -anreicherung: Dr. Jaap Geraerts&lt;/p&gt;&#10;&lt;p&gt;Langzeitverfügbarkeit: Fabian Cremer&lt;/p&gt;&#10;&lt;p&gt;Projektleitung: Thorsten Wübbena&lt;/p&gt;&#10;&#10;&#10;&lt;p class=&quot;mt-7&quot;&gt;&lt;strong&gt;Angaben gemäß § 5 TMG&lt;/strong&gt;&lt;/p&gt;&#10;&#10;&lt;p class=&quot;mt-5&quot;&gt;&lt;em&gt;Verantwortlich für den Inhalt&lt;/em&gt;&lt;/p&gt;&#10;&lt;p&gt;Leibniz-Institut für Europäische Geschichte (IEG)&lt;br&gt;&#10;Alte Universitätsstraße 19&lt;br&gt;&#10;D-55116 Mainz&lt;br&gt;&#10;&lt;a href=&quot;http://www.ieg-mainz.de&quot;&gt;http://www.ieg-mainz.de&lt;/a&gt;&#10;&lt;a href=&quot;mailto:info@ieg-mainz.de&quot;&gt;info@ieg-mainz.de&lt;/a&gt;&lt;br /&gt;&#10;Telefon: ++49 (0) 6131 39 393 50&lt;br&gt;&#10;Fax: ++ 49 (0) 6131 39 353 26&lt;/p&gt;&#10;&lt;p&gt;Prof. Dr. Nicole Reinhardt, Prof. Dr. Johannes Paulmann&lt;/p&gt;&#10;&#10;&lt;p class=&quot;mt-5&quot;&gt;&lt;em&gt;Programming and Design&lt;/em&gt;&lt;/p&gt;&#10;&#10;&lt;p&gt;Wendig OÜ&lt;br&gt;&#10;&lt;a href=&quot;https://wendig.io&quot;&gt;https://wendig.io&lt;/a&gt;&lt;/p&gt;&#10;&#10;&lt;p class=&quot;mt-5&quot;&gt;&lt;em&gt;Rechtliche Hinweise&lt;/em&gt;&lt;/p&gt;&#10;&#10;&lt;p&gt;„Europäische Friedensverträge der Vormoderne in Daten (FriVer+)“ wird gemäß deutschem Urheberrecht publiziert, dessen Schutzdauer die international vereinbarte Mindestschutzfrist der Revidierten Berner Übereinkunft (RBÜ) überschreitet und gemäß EU-Recht auf 70 Jahre nach Tod des Urhebers verlängert. Das IEG prüft sorgfältig sämtliche Rechte zur Speicherung und Veröffentlichung von urheberrechtlich geschütztem Material. Urheberrechtlich geschütztes Material, für das keine Rechteklärung erfolgen kann, wird nicht in „Ortstermine“ gespeichert oder veröffentlicht.&lt;/p&gt;&#10;&#10;&lt;p class=&quot;mt-5&quot;&gt;&lt;em&gt;Haftungsausschluss&lt;/em&gt;&lt;/p&gt;&#10;&#10;&lt;p&gt;Trotz sorgfältiger inhaltlicher Kontrolle übernimmt die herausgebende Institution keine Haftung für die Inhalte externer Links. Für den Inhalt der verlinkten Seiten sind ausschließlich deren Betreiber verantwortlich.&lt;/p&gt;"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/src/translations.xlsx
+++ b/src/translations.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="76">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -263,6 +263,24 @@
   <si>
     <t xml:space="preserve">Transkription</t>
   </si>
+  <si>
+    <t xml:space="preserve">languages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sprachen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">show_all</t>
+  </si>
+  <si>
+    <t xml:space="preserve">alle anzeigen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">active_filters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aktive Filter</t>
+  </si>
 </sst>
 </file>
 
@@ -272,7 +290,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -320,13 +338,6 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF0000FF"/>
-      <name val="Noto Sans Mono"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -377,7 +388,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -419,10 +430,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -549,7 +556,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr defaultColWidth="11.5078125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="33.52"/>
@@ -818,7 +825,7 @@
       <c r="A29" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B29" s="11" t="s">
+      <c r="B29" s="9" t="s">
         <v>63</v>
       </c>
     </row>
@@ -844,6 +851,30 @@
       </c>
       <c r="B32" s="2" t="s">
         <v>69</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/src/translations.xlsx
+++ b/src/translations.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="78">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -280,6 +280,12 @@
   </si>
   <si>
     <t xml:space="preserve">aktive Filter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reset_all_filters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">alle Filter zurücksetzen</t>
   </si>
 </sst>
 </file>
@@ -556,7 +562,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr defaultColWidth="11.5078125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="33.52"/>
@@ -875,6 +881,14 @@
       </c>
       <c r="B35" s="2" t="s">
         <v>75</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/src/translations.xlsx
+++ b/src/translations.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="80">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -286,6 +286,12 @@
   </si>
   <si>
     <t xml:space="preserve">alle Filter zurücksetzen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">back_to_super_page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zurück zur Startseite</t>
   </si>
 </sst>
 </file>
@@ -562,7 +568,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr defaultColWidth="11.5078125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="33.52"/>
@@ -889,6 +895,14 @@
       </c>
       <c r="B36" s="2" t="s">
         <v>77</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/src/translations.xlsx
+++ b/src/translations.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="82">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -292,6 +292,12 @@
   </si>
   <si>
     <t xml:space="preserve">zurück zur Startseite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">search_in_title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suche im Titel</t>
   </si>
 </sst>
 </file>
@@ -568,7 +574,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr defaultColWidth="11.5078125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="33.52"/>
@@ -903,6 +909,14 @@
       </c>
       <c r="B37" s="2" t="s">
         <v>79</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/src/translations.xlsx
+++ b/src/translations.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="86">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -298,6 +298,18 @@
   </si>
   <si>
     <t xml:space="preserve">Suche im Titel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">go_to_image</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gehe zu Abbildung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">of</t>
+  </si>
+  <si>
+    <t xml:space="preserve">von</t>
   </si>
 </sst>
 </file>
@@ -574,8 +586,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C38"/>
-  <sheetFormatPr defaultColWidth="11.5078125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:C40"/>
+  <sheetFormatPr defaultColWidth="11.5078125" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="33.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="119.79"/>
@@ -917,6 +929,22 @@
       </c>
       <c r="B38" s="2" t="s">
         <v>81</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/src/translations.xlsx
+++ b/src/translations.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="90">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -310,6 +310,18 @@
   </si>
   <si>
     <t xml:space="preserve">von</t>
+  </si>
+  <si>
+    <t xml:space="preserve">archives</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Archive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">archive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Archiv</t>
   </si>
 </sst>
 </file>
@@ -586,7 +598,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr defaultColWidth="11.5078125" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="33.52"/>
@@ -945,6 +957,22 @@
       </c>
       <c r="B40" s="2" t="s">
         <v>85</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/src/translations.xlsx
+++ b/src/translations.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="94">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -322,6 +322,18 @@
   </si>
   <si>
     <t xml:space="preserve">Archiv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abstract</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inhalt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prints</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drucke</t>
   </si>
 </sst>
 </file>
@@ -598,7 +610,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr defaultColWidth="11.5078125" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="33.52"/>
@@ -973,6 +985,22 @@
       </c>
       <c r="B42" s="2" t="s">
         <v>89</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/src/translations.xlsx
+++ b/src/translations.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="96">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -334,6 +334,12 @@
   </si>
   <si>
     <t xml:space="preserve">Drucke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">facsimile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Digitalisat / Faksimile</t>
   </si>
 </sst>
 </file>
@@ -610,7 +616,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:C45"/>
   <sheetFormatPr defaultColWidth="11.5078125" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="33.52"/>
@@ -1001,6 +1007,14 @@
       </c>
       <c r="B44" s="2" t="s">
         <v>93</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/src/translations.xlsx
+++ b/src/translations.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="98">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -340,6 +340,12 @@
   </si>
   <si>
     <t xml:space="preserve">Digitalisat / Faksimile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">download_this_image</t>
+  </si>
+  <si>
+    <t xml:space="preserve">diese Abbildung herunterladen</t>
   </si>
 </sst>
 </file>
@@ -616,7 +622,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr defaultColWidth="11.5078125" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="33.52"/>
@@ -1015,6 +1021,14 @@
       </c>
       <c r="B45" s="2" t="s">
         <v>95</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/src/translations.xlsx
+++ b/src/translations.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="100">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -346,6 +346,12 @@
   </si>
   <si>
     <t xml:space="preserve">diese Abbildung herunterladen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">styles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Facetten</t>
   </si>
 </sst>
 </file>
@@ -622,7 +628,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C46"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr defaultColWidth="11.5078125" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="33.52"/>
@@ -1029,6 +1035,14 @@
       </c>
       <c r="B46" s="2" t="s">
         <v>97</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/src/translations.xlsx
+++ b/src/translations.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="102">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -352,6 +352,12 @@
   </si>
   <si>
     <t xml:space="preserve">Facetten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">biblio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Literatur</t>
   </si>
 </sst>
 </file>
@@ -628,7 +634,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:C48"/>
   <sheetFormatPr defaultColWidth="11.5078125" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="33.52"/>
@@ -1043,6 +1049,14 @@
       </c>
       <c r="B47" s="2" t="s">
         <v>99</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/src/translations.xlsx
+++ b/src/translations.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="126">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -28,7 +28,7 @@
     <t xml:space="preserve">de</t>
   </si>
   <si>
-    <t xml:space="preserve">OLD</t>
+    <t xml:space="preserve">en</t>
   </si>
   <si>
     <t xml:space="preserve">super_title</t>
@@ -40,6 +40,9 @@
     <t xml:space="preserve">super_legacy_button</t>
   </si>
   <si>
+    <t xml:space="preserve">Altprojekt</t>
+  </si>
+  <si>
     <t xml:space="preserve">legacy project</t>
   </si>
   <si>
@@ -49,12 +52,18 @@
     <t xml:space="preserve">2005 – 2010</t>
   </si>
   <si>
+    <t xml:space="preserve">2005 - 2010</t>
+  </si>
+  <si>
     <t xml:space="preserve">super_friverplus_button</t>
   </si>
   <si>
     <t xml:space="preserve">Data (FriVer+)</t>
   </si>
   <si>
+    <t xml:space="preserve">data (FriVer+)</t>
+  </si>
+  <si>
     <t xml:space="preserve">friverplus_years</t>
   </si>
   <si>
@@ -62,9 +71,6 @@
   </si>
   <si>
     <t xml:space="preserve">Diese Website bietet Zugang zu den Daten von mehr als 1800 frühneuzeitlichen europäischen Friedensverträgen. Die Daten wurden im Rahmen des Legacy-Projekts &lt;a href="https://www.ieg-friedensvertraege.de/Startseite------_site.index..html_dir._nav.2_likecms.html"&gt;Europäische Friedensverträge der Vormoderne online&lt;/a&gt; gesammelt. Im Jahr 2023 wurden diese Daten im Rahmen des Projekts &lt;a href="https://www.ieg-friedensvertraege.de/friverplus"&gt;Europäische Friedensverträge der Vormoderne in Daten (FriVer+)&lt;/a&gt; in XML umgewandelt. Die Daten umfassen digitale Surrogate, Metadaten und in einer begrenzten Anzahl von Fällen auch Editionen und Transliterationen der Texte.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This site provides access to data pertaining to more than 1800 early modern European peace treaties. The data was gathered by the legacy project &lt;a href="https://www.ieg-friedensvertraege.de/Startseite------_site.index..html_dir._nav.2_likecms.html"&gt;Europäische Friedensverträge der Vormoderne online&lt;/a&gt; (2005-2010). In 2023 this data was transformed into XML as part of the &lt;a href="https://www.ieg-friedensvertraege.de/friverplus"&gt;Europäische Friedensverträge der Vormoderne in Daten (FriVer+)&lt;/a&gt; project. The data comprises digital surrogates, metadata, and, in a more limited number of cases, editions and transliterations of the texts as well.</t>
   </si>
   <si>
     <t xml:space="preserve">friverplus_short_title</t>
@@ -252,6 +258,9 @@
     <t xml:space="preserve">Datenschutz</t>
   </si>
   <si>
+    <t xml:space="preserve">data privacy</t>
+  </si>
+  <si>
     <t xml:space="preserve">edition</t>
   </si>
   <si>
@@ -264,6 +273,9 @@
     <t xml:space="preserve">Transkription</t>
   </si>
   <si>
+    <t xml:space="preserve">transcription</t>
+  </si>
+  <si>
     <t xml:space="preserve">languages</t>
   </si>
   <si>
@@ -276,36 +288,54 @@
     <t xml:space="preserve">alle anzeigen</t>
   </si>
   <si>
+    <t xml:space="preserve">show all</t>
+  </si>
+  <si>
     <t xml:space="preserve">active_filters</t>
   </si>
   <si>
     <t xml:space="preserve">aktive Filter</t>
   </si>
   <si>
+    <t xml:space="preserve">active filters</t>
+  </si>
+  <si>
     <t xml:space="preserve">reset_all_filters</t>
   </si>
   <si>
     <t xml:space="preserve">alle Filter zurücksetzen</t>
   </si>
   <si>
+    <t xml:space="preserve">reset</t>
+  </si>
+  <si>
     <t xml:space="preserve">back_to_super_page</t>
   </si>
   <si>
     <t xml:space="preserve">zurück zur Startseite</t>
   </si>
   <si>
+    <t xml:space="preserve">back to start page</t>
+  </si>
+  <si>
     <t xml:space="preserve">search_in_title</t>
   </si>
   <si>
     <t xml:space="preserve">Suche im Titel</t>
   </si>
   <si>
+    <t xml:space="preserve">search in title</t>
+  </si>
+  <si>
     <t xml:space="preserve">go_to_image</t>
   </si>
   <si>
     <t xml:space="preserve">gehe zu Abbildung</t>
   </si>
   <si>
+    <t xml:space="preserve">go to image</t>
+  </si>
+  <si>
     <t xml:space="preserve">of</t>
   </si>
   <si>
@@ -348,16 +378,58 @@
     <t xml:space="preserve">diese Abbildung herunterladen</t>
   </si>
   <si>
+    <t xml:space="preserve">download this image</t>
+  </si>
+  <si>
     <t xml:space="preserve">styles</t>
   </si>
   <si>
     <t xml:space="preserve">Facetten</t>
   </si>
   <si>
+    <t xml:space="preserve">facets</t>
+  </si>
+  <si>
     <t xml:space="preserve">biblio</t>
   </si>
   <si>
     <t xml:space="preserve">Literatur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bibliography</t>
+  </si>
+  <si>
+    <t xml:space="preserve">legacy_record</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ehemaliger Datensatz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">legacy record</t>
+  </si>
+  <si>
+    <t xml:space="preserve">show</t>
+  </si>
+  <si>
+    <t xml:space="preserve">anzeigen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">download</t>
+  </si>
+  <si>
+    <t xml:space="preserve">herunterladen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">entries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Einträge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seite</t>
   </si>
 </sst>
 </file>
@@ -466,7 +538,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -497,6 +569,10 @@
     </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -531,37 +607,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -634,7 +710,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C53"/>
   <sheetFormatPr defaultColWidth="11.5078125" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="33.52"/>
@@ -671,392 +747,535 @@
       <c r="B3" s="7" t="s">
         <v>6</v>
       </c>
+      <c r="C3" s="7" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>2023</v>
       </c>
+      <c r="C6" s="8" t="n">
+        <v>2023</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="313.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>14</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="C7" s="7"/>
     </row>
     <row r="8" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="346.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="288.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="33.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>24</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="33.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="33.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="33.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="408.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B29" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>73</v>
+        <v>77</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>75</v>
+        <v>80</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>79</v>
+        <v>86</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>81</v>
+        <v>89</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>83</v>
+        <v>92</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>85</v>
+        <v>95</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>87</v>
+        <v>97</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>89</v>
+        <v>99</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>91</v>
+        <v>101</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>93</v>
+        <v>103</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>97</v>
+        <v>107</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>99</v>
+        <v>110</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>101</v>
+        <v>113</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>124</v>
       </c>
     </row>
   </sheetData>

--- a/src/translations.xlsx
+++ b/src/translations.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="128">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -430,6 +430,12 @@
   </si>
   <si>
     <t xml:space="preserve">Seite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">footnotes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fußnoten</t>
   </si>
 </sst>
 </file>
@@ -710,7 +716,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C53"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr defaultColWidth="11.5078125" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="33.52"/>
@@ -784,7 +790,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="313.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="149.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
@@ -1276,6 +1282,17 @@
       </c>
       <c r="C53" s="1" t="s">
         <v>124</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>126</v>
       </c>
     </row>
   </sheetData>

--- a/src/translations.xlsx
+++ b/src/translations.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="133">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -215,43 +215,6 @@
     <t xml:space="preserve">Quelle</t>
   </si>
   <si>
-    <t xml:space="preserve">imprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Impressum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">imprint_text</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p class="mt-4"&gt;&lt;em&gt;Herausgebende Institution&lt;/em&gt;&lt;/p&gt;
-&lt;p&gt;Leibniz-Institut für Europäische Geschichte (IEG)&lt;br&gt;
-Alte Universitätsstraße 19&lt;br&gt;
-D-55116 Mainz&lt;br&gt;
-&lt;p&gt;Gefördert im Rahmen der 2. Ausschreibungsrunde (2023) „Kooperationsprojekte“ des NFDI-Konsortiums text+ (&lt;a href="https://text-plus.org"&gt;https://text-plus.org&lt;/a&gt;)&lt;/p&gt;
-&lt;p class="mt-4"&gt;&lt;em&gt;Projektteam am IEG&lt;/em&gt;&lt;/p&gt;
-&lt;p&gt;Editorische Verantwortung, Datenbereinigung, -transformation, -anreicherung: Dr. Jaap Geraerts&lt;/p&gt;
-&lt;p&gt;Langzeitverfügbarkeit: Fabian Cremer&lt;/p&gt;
-&lt;p&gt;Projektleitung: Thorsten Wübbena&lt;/p&gt;
-&lt;p class="mt-7"&gt;&lt;strong&gt;Angaben gemäß § 5 TMG&lt;/strong&gt;&lt;/p&gt;
-&lt;p class="mt-5"&gt;&lt;em&gt;Verantwortlich für den Inhalt&lt;/em&gt;&lt;/p&gt;
-&lt;p&gt;Leibniz-Institut für Europäische Geschichte (IEG)&lt;br&gt;
-Alte Universitätsstraße 19&lt;br&gt;
-D-55116 Mainz&lt;br&gt;
-&lt;a href="http://www.ieg-mainz.de"&gt;http://www.ieg-mainz.de&lt;/a&gt;
-&lt;a href="mailto:info@ieg-mainz.de"&gt;info@ieg-mainz.de&lt;/a&gt;&lt;br /&gt;
-Telefon: ++49 (0) 6131 39 393 50&lt;br&gt;
-Fax: ++ 49 (0) 6131 39 353 26&lt;/p&gt;
-&lt;p&gt;Prof. Dr. Nicole Reinhardt, Prof. Dr. Johannes Paulmann&lt;/p&gt;
-&lt;p class="mt-5"&gt;&lt;em&gt;Programming and Design&lt;/em&gt;&lt;/p&gt;
-&lt;p&gt;Wendig OÜ&lt;br&gt;
-&lt;a href="https://wendig.io"&gt;https://wendig.io&lt;/a&gt;&lt;/p&gt;
-&lt;p class="mt-5"&gt;&lt;em&gt;Rechtliche Hinweise&lt;/em&gt;&lt;/p&gt;
-&lt;p&gt;„Europäische Friedensverträge der Vormoderne in Daten (FriVer+)“ wird gemäß deutschem Urheberrecht publiziert, dessen Schutzdauer die international vereinbarte Mindestschutzfrist der Revidierten Berner Übereinkunft (RBÜ) überschreitet und gemäß EU-Recht auf 70 Jahre nach Tod des Urhebers verlängert. Das IEG prüft sorgfältig sämtliche Rechte zur Speicherung und Veröffentlichung von urheberrechtlich geschütztem Material. Urheberrechtlich geschütztes Material, für das keine Rechteklärung erfolgen kann, wird nicht in „Ortstermine“ gespeichert oder veröffentlicht.&lt;/p&gt;
-&lt;p class="mt-5"&gt;&lt;em&gt;Haftungsausschluss&lt;/em&gt;&lt;/p&gt;
-&lt;p&gt;Trotz sorgfältiger inhaltlicher Kontrolle übernimmt die herausgebende Institution keine Haftung für die Inhalte externer Links. Für den Inhalt der verlinkten Seiten sind ausschließlich deren Betreiber verantwortlich.&lt;/p&gt;</t>
-  </si>
-  <si>
     <t xml:space="preserve">privacy</t>
   </si>
   <si>
@@ -436,6 +399,33 @@
   </si>
   <si>
     <t xml:space="preserve">Fußnoten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">to_search</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zur Suche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search</t>
+  </si>
+  <si>
+    <t xml:space="preserve">about</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Über das Projekt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">about this project</t>
+  </si>
+  <si>
+    <t xml:space="preserve">to_docs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zur Projektdokumentation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Documentation</t>
   </si>
 </sst>
 </file>
@@ -716,7 +706,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C1048576"/>
   <sheetFormatPr defaultColWidth="11.5078125" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="33.52"/>
@@ -1009,111 +999,114 @@
         <v>63</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="408.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B29" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C29" s="1" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>90</v>
@@ -1121,13 +1114,13 @@
     </row>
     <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B39" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C39" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1182,48 +1175,48 @@
         <v>103</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>114</v>
@@ -1231,13 +1224,13 @@
     </row>
     <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B49" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C49" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1281,24 +1274,36 @@
         <v>125</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
+        <v>129</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B11" r:id="rId1" display="&lt;a href=&quot;https://www.text-plus.org/&quot;&gt;TEXT+&lt;/a&gt;"/>
-    <hyperlink ref="B29" r:id="rId2" display="&lt;p class=&quot;mt-4&quot;&gt;&lt;em&gt;Herausgebende Institution&lt;/em&gt;&lt;/p&gt;&#10;&#10;&lt;p&gt;Leibniz-Institut für Europäische Geschichte (IEG)&lt;br&gt;&#10;Alte Universitätsstraße 19&lt;br&gt;&#10;D-55116 Mainz&lt;br&gt;&#10;&#10;&lt;p&gt;Gefördert im Rahmen der 2. Ausschreibungsrunde (2023) „Kooperationsprojekte“ des NFDI-Konsortiums text+ (&lt;a href=&quot;https://text-plus.org&quot;&gt;https://text-plus.org&lt;/a&gt;)&lt;/p&gt;&#10;&#10;&lt;p class=&quot;mt-4&quot;&gt;&lt;em&gt;Projektteam am IEG&lt;/em&gt;&lt;/p&gt;&#10;&#10;&lt;p&gt;Editorische Verantwortung, Datenbereinigung, -transformation, -anreicherung: Dr. Jaap Geraerts&lt;/p&gt;&#10;&lt;p&gt;Langzeitverfügbarkeit: Fabian Cremer&lt;/p&gt;&#10;&lt;p&gt;Projektleitung: Thorsten Wübbena&lt;/p&gt;&#10;&#10;&#10;&lt;p class=&quot;mt-7&quot;&gt;&lt;strong&gt;Angaben gemäß § 5 TMG&lt;/strong&gt;&lt;/p&gt;&#10;&#10;&lt;p class=&quot;mt-5&quot;&gt;&lt;em&gt;Verantwortlich für den Inhalt&lt;/em&gt;&lt;/p&gt;&#10;&lt;p&gt;Leibniz-Institut für Europäische Geschichte (IEG)&lt;br&gt;&#10;Alte Universitätsstraße 19&lt;br&gt;&#10;D-55116 Mainz&lt;br&gt;&#10;&lt;a href=&quot;http://www.ieg-mainz.de&quot;&gt;http://www.ieg-mainz.de&lt;/a&gt;&#10;&lt;a href=&quot;mailto:info@ieg-mainz.de&quot;&gt;info@ieg-mainz.de&lt;/a&gt;&lt;br /&gt;&#10;Telefon: ++49 (0) 6131 39 393 50&lt;br&gt;&#10;Fax: ++ 49 (0) 6131 39 353 26&lt;/p&gt;&#10;&lt;p&gt;Prof. Dr. Nicole Reinhardt, Prof. Dr. Johannes Paulmann&lt;/p&gt;&#10;&#10;&lt;p class=&quot;mt-5&quot;&gt;&lt;em&gt;Programming and Design&lt;/em&gt;&lt;/p&gt;&#10;&#10;&lt;p&gt;Wendig OÜ&lt;br&gt;&#10;&lt;a href=&quot;https://wendig.io&quot;&gt;https://wendig.io&lt;/a&gt;&lt;/p&gt;&#10;&#10;&lt;p class=&quot;mt-5&quot;&gt;&lt;em&gt;Rechtliche Hinweise&lt;/em&gt;&lt;/p&gt;&#10;&#10;&lt;p&gt;„Europäische Friedensverträge der Vormoderne in Daten (FriVer+)“ wird gemäß deutschem Urheberrecht publiziert, dessen Schutzdauer die international vereinbarte Mindestschutzfrist der Revidierten Berner Übereinkunft (RBÜ) überschreitet und gemäß EU-Recht auf 70 Jahre nach Tod des Urhebers verlängert. Das IEG prüft sorgfältig sämtliche Rechte zur Speicherung und Veröffentlichung von urheberrechtlich geschütztem Material. Urheberrechtlich geschütztes Material, für das keine Rechteklärung erfolgen kann, wird nicht in „Ortstermine“ gespeichert oder veröffentlicht.&lt;/p&gt;&#10;&#10;&lt;p class=&quot;mt-5&quot;&gt;&lt;em&gt;Haftungsausschluss&lt;/em&gt;&lt;/p&gt;&#10;&#10;&lt;p&gt;Trotz sorgfältiger inhaltlicher Kontrolle übernimmt die herausgebende Institution keine Haftung für die Inhalte externer Links. Für den Inhalt der verlinkten Seiten sind ausschließlich deren Betreiber verantwortlich.&lt;/p&gt;"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/src/translations.xlsx
+++ b/src/translations.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="135">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -426,6 +426,12 @@
   </si>
   <si>
     <t xml:space="preserve">Documentation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">toc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">table of contents</t>
   </si>
 </sst>
 </file>
@@ -1299,6 +1305,17 @@
         <v>132</v>
       </c>
     </row>
+    <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>

--- a/src/translations.xlsx
+++ b/src/translations.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="135">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -716,8 +716,8 @@
   <sheetFormatPr defaultColWidth="11.5078125" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="33.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="119.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="53.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="80.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="73.18"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="11.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="83"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="6" style="3" width="11.5"/>
@@ -934,11 +934,14 @@
         <v>48</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="83.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B22" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C22" s="7" t="s">
         <v>51</v>
       </c>
     </row>

--- a/src/translations.xlsx
+++ b/src/translations.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\facremer\git\friverxqtei\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A72FEA1-87FC-44DE-AD7E-CF5550359356}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCED1D81-0C34-491A-8E36-9718EDA7E273}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="translations" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="143">
   <si>
     <t>id</t>
   </si>
@@ -456,6 +456,11 @@
     <t>This website provides information on a total of 1800 European peace treaties from the period between 1400 and 1789. The data include metadata of the treaties, digitized sources, and, in a limited number of cases, also transcriptions and editions of the texts as well as references to available printed works.&lt;br&gt;&lt;br&gt;
 The online database and the research data collection are maintained and curated by the &lt;a href="https://www.ieg-mainz.de"&gt;Leibniz Institute for European History (IEG)&lt;/a&gt;. The database was&lt;ul&gt;&lt;li&gt;established by the DFG-funded project &lt;a href="https://www.ieg-mainz.de/ieg-digital/europaeische-friedensvertraege-der-vormoderne-online/"&gt;“European Peace Treaties of the Premodern Era Online” (2005–2010)&lt;/a&gt;,&lt;/li&gt;&lt;li&gt;expanded within the &lt;a href="https://www.text-plus.org/"&gt;Text+&lt;/a&gt; cooperation project &lt;a href="https://www.ieg-mainz.de/research/research-projects/europaeische-friedensvertraege-der-vormoderne-in-daten-friver/"&gt;“FriVer+ (European Peace Treaties of the Premodern Era in Data, 2023)”&lt;/a&gt; as a standardized and enriched edition,&lt;/li&gt;&lt;li&gt;and has been continuously maintained since 2026 with a new database within the framework of &lt;a href="https://www.ieg-mainz.de/publikationen/ieg-digital/"&gt;IEG digital&lt;/a&gt;.&lt;/li&gt;&lt;/ul&gt;&lt;br&gt;
 In the associated &lt;a href="/page/publication-portal"&gt;Publication Portal European Peace Treaties&lt;/a&gt;, results of historical peace research on the premodern era have been published from various disciplinary perspectives (including history, international law, political science, linguistics, and art history).</t>
+  </si>
+  <si>
+    <t>This website provides access to data on more than 1,800 early modern European peace treaties. The online database brings together a cultural heritage that is scattered across archives throughout Europe, is difficult to access, and in some cases has not yet been cataloged.&lt;br&gt;&lt;br&gt;
+The treaties published here are mostly negotiators’ copies, but also – based on historical records – ratifications and transcripts. In some cases, the sources have been supplemented with printed versions.&lt;br&gt;&lt;br&gt;
+The online database provides easy access to the treaties and allows for direct analysis of the fully freely available database.</t>
   </si>
 </sst>
 </file>
@@ -752,7 +757,7 @@
         <v>122</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>122</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8" spans="1:3">
